--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487619_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487619_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. VICENTE VIANA</t>
+          <t>C. KLOTZ MAROTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6118</v>
+        <v>2.2594</v>
       </c>
       <c r="E2" t="n">
-        <v>4.099</v>
+        <v>1.3867</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4872</v>
+        <v>0.8727</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.064</v>
+        <v>2.9963</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5709</v>
+        <v>1.1806</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.4931</v>
+        <v>1.8157</v>
       </c>
       <c r="J2" t="n">
-        <v>1.0039</v>
+        <v>3.3926</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6385</v>
+        <v>1.4212</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3654</v>
+        <v>1.9715</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.0679</v>
+        <v>-0.3963</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.2095</v>
+        <v>-0.2406</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.8585</v>
+        <v>-0.1557</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7164</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>-1.9403</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7164</v>
+        <v>1.9403</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7833</v>
+        <v>-0.4548</v>
       </c>
       <c r="T2" t="n">
-        <v>1.919</v>
+        <v>-0.06560000000000001</v>
       </c>
       <c r="U2" t="n">
-        <v>0.8643</v>
+        <v>-0.3892</v>
       </c>
       <c r="V2" t="n">
-        <v>1.1761</v>
+        <v>-0.2821</v>
       </c>
       <c r="W2" t="n">
-        <v>1.1761</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. KLOTZ MAROTO</t>
+          <t>A. VICENTE VIANA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.611</v>
+        <v>1.8564</v>
       </c>
       <c r="E3" t="n">
-        <v>1.0654</v>
+        <v>3.0795</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5457</v>
+        <v>-1.223</v>
       </c>
       <c r="G3" t="n">
-        <v>2.9963</v>
+        <v>-3.064</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1806</v>
+        <v>-0.5709</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8157</v>
+        <v>-2.4931</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3926</v>
+        <v>1.0039</v>
       </c>
       <c r="K3" t="n">
-        <v>1.4212</v>
+        <v>0.6385</v>
       </c>
       <c r="L3" t="n">
-        <v>1.9715</v>
+        <v>0.3654</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.3963</v>
+        <v>-4.0679</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.2406</v>
+        <v>-1.2095</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1557</v>
+        <v>-2.8585</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2.7164</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9403</v>
+        <v>2.7164</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1032</v>
+        <v>1.0279</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.387</v>
+        <v>0.8995</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.7161999999999999</v>
+        <v>0.1285</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2821</v>
+        <v>1.1761</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.1761</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3599</v>
+        <v>0.6418</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7877999999999999</v>
+        <v>-0.5876</v>
       </c>
       <c r="F4" t="n">
-        <v>1.1477</v>
+        <v>1.2295</v>
       </c>
       <c r="G4" t="n">
         <v>-0.3392</v>
@@ -766,13 +766,13 @@
         <v>0.5821</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2607</v>
+        <v>0.0213</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1817</v>
+        <v>0.0185</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.079</v>
+        <v>0.0028</v>
       </c>
       <c r="V4" t="n">
         <v>0.3776</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. BALDAN MARTÍN</t>
+          <t>C. UNANUE CEGARRA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.2365</v>
+        <v>0.1104</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1611</v>
+        <v>2.596</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.07539999999999999</v>
+        <v>-2.4856</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2694</v>
+        <v>-1.0297</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.4029</v>
+        <v>-1.7482</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1335</v>
+        <v>0.7185</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0206</v>
+        <v>3.2673</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0206</v>
+        <v>0.0907</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.1766</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.29</v>
+        <v>-4.297</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4235</v>
+        <v>-1.8389</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1335</v>
+        <v>-2.4581</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.1642</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.1344</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3149</v>
+        <v>-0.0241</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1817</v>
+        <v>0.2989</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4966</v>
+        <v>-0.323</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2821</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2543</v>
+        <v>-0.2271</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2543</v>
+        <v>-0.2271</v>
       </c>
       <c r="G6" t="n">
         <v>-0.2725</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. ABOUBACAR HIMA</t>
+          <t>M. BALDAN MARTÍN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3562</v>
+        <v>-0.3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6533</v>
+        <v>-0.061</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0095</v>
+        <v>-0.239</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.1468</v>
+        <v>-0.2694</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7703</v>
+        <v>-0.4029</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3765</v>
+        <v>0.1335</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0047</v>
+        <v>0.0206</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0453</v>
+        <v>0.0206</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0406</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1421</v>
+        <v>-0.29</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.725</v>
+        <v>-0.4235</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4171</v>
+        <v>0.1335</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5821</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3881</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.1332</v>
+        <v>0.2515</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1222</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2555</v>
+        <v>0.3331</v>
       </c>
       <c r="V7" t="n">
-        <v>1.506</v>
+        <v>-0.2821</v>
       </c>
       <c r="W7" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. UNANUE CEGARRA</t>
+          <t>S. ABOUBACAR HIMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4351</v>
+        <v>-0.4114</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2141</v>
+        <v>0.4346</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6492</v>
+        <v>-0.846</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.0297</v>
+        <v>-1.1468</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.7482</v>
+        <v>-0.7703</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7185</v>
+        <v>-0.3765</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2673</v>
+        <v>-0.0047</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0907</v>
+        <v>-0.0453</v>
       </c>
       <c r="L8" t="n">
-        <v>3.1766</v>
+        <v>0.0406</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.297</v>
+        <v>-1.1421</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8389</v>
+        <v>-0.725</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.4581</v>
+        <v>-0.4171</v>
       </c>
       <c r="P8" t="n">
-        <v>1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1344</v>
+        <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5695</v>
+        <v>-0.1884</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.083</v>
+        <v>-0.0965</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4865</v>
+        <v>-0.092</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.506</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2148</v>
+        <v>-0.6509</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1145</v>
+        <v>-0.7141</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1003</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="G9" t="n">
         <v>0.0882</v>
@@ -1156,13 +1156,13 @@
         <v>1.3582</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3149</v>
+        <v>0.249</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5933</v>
+        <v>-0.1929</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2784</v>
+        <v>0.4419</v>
       </c>
       <c r="V9" t="n">
         <v>0.5642</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8901</v>
+        <v>-2.1382</v>
       </c>
       <c r="E10" t="n">
-        <v>1.9733</v>
+        <v>2.1339</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.8633</v>
+        <v>-4.2721</v>
       </c>
       <c r="G10" t="n">
         <v>-0.7196</v>
@@ -1234,13 +1234,13 @@
         <v>1.5523</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3937</v>
+        <v>0.1455</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1806</v>
+        <v>-0.0199</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5743</v>
+        <v>0.1655</v>
       </c>
       <c r="V10" t="n">
         <v>-1.1761</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7994</v>
+        <v>-6.9906</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.5361</v>
+        <v>-3.8364</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2633</v>
+        <v>-3.1543</v>
       </c>
       <c r="G11" t="n">
         <v>-5.1354</v>
@@ -1312,13 +1312,13 @@
         <v>1.5523</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6076</v>
+        <v>0.4164</v>
       </c>
       <c r="T11" t="n">
-        <v>0.766</v>
+        <v>0.4657</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1584</v>
+        <v>-0.0493</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8836</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.8393</v>
+        <v>-7.6843</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3118</v>
+        <v>-2.4294</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.5274</v>
+        <v>-5.2549</v>
       </c>
       <c r="G12" t="n">
         <v>-1.6236</v>
@@ -1390,13 +1390,13 @@
         <v>2.3284</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.9157</v>
+        <v>-0.7607</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.0655</v>
+        <v>-0.1831</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8501</v>
+        <v>-0.5776</v>
       </c>
       <c r="V12" t="n">
         <v>-2.7776</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-14.443</v>
+        <v>-13.5345</v>
       </c>
       <c r="E13" t="n">
-        <v>1.093800000000002</v>
+        <v>2.002200000000002</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.5365</v>
+        <v>-15.5366</v>
       </c>
       <c r="G13" t="n">
         <v>-10.5157</v>
@@ -1468,13 +1468,13 @@
         <v>14.5525</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1794999999999998</v>
+        <v>0.729</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1344000000000001</v>
+        <v>1.043</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.3139</v>
+        <v>-0.3139000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>-2.777600000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.5384</v>
+        <v>7.2301</v>
       </c>
       <c r="E14" t="n">
-        <v>6.3795</v>
+        <v>6.7799</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1589</v>
+        <v>0.4502</v>
       </c>
       <c r="G14" t="n">
         <v>4.7413</v>
@@ -1546,13 +1546,13 @@
         <v>2.3284</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4865</v>
+        <v>0.2053</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.387</v>
+        <v>0.0134</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.09950000000000001</v>
+        <v>0.1918</v>
       </c>
       <c r="V14" t="n">
         <v>3.0597</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.1475</v>
+        <v>6.0179</v>
       </c>
       <c r="E15" t="n">
-        <v>5.822</v>
+        <v>6.0222</v>
       </c>
       <c r="F15" t="n">
-        <v>0.3256</v>
+        <v>-0.0043</v>
       </c>
       <c r="G15" t="n">
         <v>5.8434</v>
@@ -1624,13 +1624,13 @@
         <v>2.3284</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0236</v>
+        <v>0.8939</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0987</v>
+        <v>0.2989</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9249000000000001</v>
+        <v>0.595</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8836</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.042</v>
+        <v>4.0809</v>
       </c>
       <c r="E16" t="n">
-        <v>4.4133</v>
+        <v>3.9129</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3714</v>
+        <v>0.1681</v>
       </c>
       <c r="G16" t="n">
         <v>1.3917</v>
@@ -1702,13 +1702,13 @@
         <v>2.1344</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.0482</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6808</v>
+        <v>0.1803</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.729</v>
+        <v>-0.1895</v>
       </c>
       <c r="V16" t="n">
         <v>0.5642</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.0505</v>
+        <v>3.1361</v>
       </c>
       <c r="E17" t="n">
-        <v>1.832</v>
+        <v>2.4326</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2185</v>
+        <v>0.7035</v>
       </c>
       <c r="G17" t="n">
         <v>0.5909</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9583</v>
+        <v>0.1273</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.387</v>
+        <v>0.2136</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5713</v>
+        <v>-0.0863</v>
       </c>
       <c r="V17" t="n">
         <v>1.8358</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. NIANG</t>
+          <t>A. JIMENEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9226</v>
+        <v>0.6525</v>
       </c>
       <c r="E18" t="n">
-        <v>0.3834</v>
+        <v>0.1691</v>
       </c>
       <c r="F18" t="n">
-        <v>0.5392</v>
+        <v>0.4834</v>
       </c>
       <c r="G18" t="n">
-        <v>0.54</v>
+        <v>0.7405</v>
       </c>
       <c r="H18" t="n">
-        <v>1.9081</v>
+        <v>-0.0948</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.3681</v>
+        <v>0.8353</v>
       </c>
       <c r="J18" t="n">
-        <v>1.9714</v>
+        <v>1.4421</v>
       </c>
       <c r="K18" t="n">
-        <v>1.5654</v>
+        <v>0.0618</v>
       </c>
       <c r="L18" t="n">
-        <v>0.406</v>
+        <v>1.3803</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.4313</v>
+        <v>-0.7015</v>
       </c>
       <c r="N18" t="n">
-        <v>0.3427</v>
+        <v>-0.1565</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.774</v>
+        <v>-0.545</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.3284</v>
+        <v>-0.194</v>
       </c>
       <c r="Q18" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>1.1095</v>
+        <v>0.106</v>
       </c>
       <c r="T18" t="n">
-        <v>1.0688</v>
+        <v>-0.3028</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0406</v>
+        <v>0.4088</v>
       </c>
       <c r="V18" t="n">
-        <v>1.6015</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2239</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. JIMENEZ FERNANDEZ</t>
+          <t>M. NIANG</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6252</v>
+        <v>0.4494</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1691</v>
+        <v>-0.1171</v>
       </c>
       <c r="F19" t="n">
-        <v>0.4561</v>
+        <v>0.5664</v>
       </c>
       <c r="G19" t="n">
-        <v>0.7405</v>
+        <v>0.54</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0948</v>
+        <v>1.9081</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8353</v>
+        <v>-1.3681</v>
       </c>
       <c r="J19" t="n">
-        <v>1.4421</v>
+        <v>1.9714</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0618</v>
+        <v>1.5654</v>
       </c>
       <c r="L19" t="n">
-        <v>1.3803</v>
+        <v>0.406</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7015</v>
+        <v>-1.4313</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.1565</v>
+        <v>0.3427</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.545</v>
+        <v>-1.774</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.194</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9702</v>
+        <v>-3.8806</v>
       </c>
       <c r="R19" t="n">
-        <v>0.7761</v>
+        <v>1.5523</v>
       </c>
       <c r="S19" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.6362</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3028</v>
+        <v>0.5683</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3816</v>
+        <v>0.0679</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.6015</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.2239</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3568</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.4084</v>
+        <v>-0.0921</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0516</v>
+        <v>0.1636</v>
       </c>
       <c r="G20" t="n">
         <v>-0.6718</v>
@@ -2014,13 +2014,13 @@
         <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7465000000000001</v>
+        <v>0.4612</v>
       </c>
       <c r="T20" t="n">
-        <v>0.6684</v>
+        <v>0.1679</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0781</v>
+        <v>0.2933</v>
       </c>
       <c r="V20" t="n">
         <v>0.2821</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>E. GARCÍA PEREZ</t>
+          <t>Y. RODRÍGUEZ MACHÍN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.3798</v>
+        <v>0.0149</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3563</v>
+        <v>-0.323</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.7361</v>
+        <v>0.338</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.2978</v>
+        <v>-0.2008</v>
       </c>
       <c r="H21" t="n">
-        <v>0.3806</v>
+        <v>-0.4622</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6785</v>
+        <v>0.2614</v>
       </c>
       <c r="J21" t="n">
-        <v>0.6591</v>
+        <v>0.0948</v>
       </c>
       <c r="K21" t="n">
-        <v>0.6591</v>
+        <v>0.0948</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.9569</v>
+        <v>-0.2956</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2785</v>
+        <v>-0.5569</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6785</v>
+        <v>0.2614</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3881</v>
+        <v>1.1642</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.194</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.188</v>
+        <v>-0.0544</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.3028</v>
+        <v>-0.2238</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1149</v>
+        <v>0.1694</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. RODRÍGUEZ MACHÍN</t>
+          <t>E. GARCÍA PEREZ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.5856</v>
+        <v>-0.4616</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5232</v>
+        <v>0.3563</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0624</v>
+        <v>-0.8179</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2008</v>
+        <v>-0.2978</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.4622</v>
+        <v>0.3806</v>
       </c>
       <c r="I22" t="n">
-        <v>0.2614</v>
+        <v>-0.6785</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0948</v>
+        <v>0.6591</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0948</v>
+        <v>0.6591</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.2956</v>
+        <v>-0.9569</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.5569</v>
+        <v>-0.2785</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2614</v>
+        <v>-0.6785</v>
       </c>
       <c r="P22" t="n">
-        <v>1.1642</v>
+        <v>0.3881</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.194</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.655</v>
+        <v>-0.2697</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.424</v>
+        <v>-0.3028</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.231</v>
+        <v>0.0331</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.5633</v>
+        <v>-2.1356</v>
       </c>
       <c r="E23" t="n">
         <v>-1.9585</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6048</v>
+        <v>-0.1772</v>
       </c>
       <c r="G23" t="n">
         <v>-1.4049</v>
@@ -2248,13 +2248,13 @@
         <v>0.5821</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5763</v>
+        <v>-0.1486</v>
       </c>
       <c r="T23" t="n">
         <v>-0.2299</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3463</v>
+        <v>0.0813</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,10 +2281,10 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.7113</v>
+        <v>-2.6112</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.7457</v>
+        <v>-1.6456</v>
       </c>
       <c r="F24" t="n">
         <v>-0.9656</v>
@@ -2326,10 +2326,10 @@
         <v>0.3881</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1335</v>
+        <v>0.2336</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1694</v>
+        <v>-0.0693</v>
       </c>
       <c r="U24" t="n">
         <v>0.3028</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>14.443</v>
+        <v>16.4449</v>
       </c>
       <c r="E25" t="n">
-        <v>15.5366</v>
+        <v>15.5367</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0936</v>
+        <v>0.9082000000000001</v>
       </c>
       <c r="G25" t="n">
         <v>10.5158</v>
       </c>
       <c r="H25" t="n">
-        <v>8.485800000000001</v>
+        <v>8.485799999999998</v>
       </c>
       <c r="I25" t="n">
         <v>2.0299</v>
@@ -2380,7 +2380,7 @@
         <v>22.9053</v>
       </c>
       <c r="K25" t="n">
-        <v>9.252299999999998</v>
+        <v>9.2523</v>
       </c>
       <c r="L25" t="n">
         <v>13.6531</v>
@@ -2395,7 +2395,7 @@
         <v>-11.623</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9702999999999996</v>
       </c>
       <c r="Q25" t="n">
         <v>-14.5524</v>
@@ -2404,16 +2404,16 @@
         <v>15.5227</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1795</v>
+        <v>2.1815</v>
       </c>
       <c r="T25" t="n">
-        <v>0.3137999999999999</v>
+        <v>0.3138</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1342</v>
+        <v>1.8676</v>
       </c>
       <c r="V25" t="n">
-        <v>2.7776</v>
+        <v>2.777600000000001</v>
       </c>
       <c r="W25" t="n">
         <v>6.870200000000001</v>
